--- a/Treinamento/DuplicadoRecibos.xlsx
+++ b/Treinamento/DuplicadoRecibos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357A5260-A60E-4C0E-83FF-25583EDBAD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B1C0EC-769F-44B1-9A63-C59BC004521E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5934,31 +5934,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/DuplicadoRecibos.xlsx
+++ b/Treinamento/DuplicadoRecibos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906FF1A6-1C36-4F88-962F-13C0F6077A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2313032-6F35-4753-B337-7174C548DEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="153">
   <si>
     <t>msg</t>
   </si>
@@ -96,12 +96,21 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>175723547</t>
+  </si>
+  <si>
+    <t>21/01/2026</t>
+  </si>
+  <si>
     <t>Sim</t>
   </si>
   <si>
     <t>Apólice</t>
   </si>
   <si>
+    <t>126665960</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
@@ -111,42 +120,21 @@
     <t>7-Outros</t>
   </si>
   <si>
+    <t>Captura de parcela rejeitada - Apólice 126665960 - LUCAS ANDREI VICHIETTI</t>
+  </si>
+  <si>
+    <t>paula.ebbing@liencorretora.com.br</t>
+  </si>
+  <si>
     <t>57</t>
   </si>
   <si>
     <t>5705</t>
   </si>
   <si>
-    <t>maxsegur@maxsegur.com.br</t>
-  </si>
-  <si>
-    <t>sustentare@sustentareseguros.com.br</t>
-  </si>
-  <si>
-    <t>am@amirandacorretora.com.br</t>
-  </si>
-  <si>
-    <t>backoffice1@multicontratar.com.br</t>
-  </si>
-  <si>
-    <t>prosegrs@proseg.com.br</t>
-  </si>
-  <si>
-    <t>198854022</t>
-  </si>
-  <si>
-    <t>20/01/2026</t>
-  </si>
-  <si>
-    <t>135223383</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135223383 - WALERIO FLORES DA SILVA</t>
-  </si>
-  <si>
     <t>Prezado(a), _x000D_
 _x000D_
-Identificamos uma falha no processo de cobrança da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+Identificamos uma falha no processo de cobrança da parcela 12 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
 _x000D_
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
 _x000D_
@@ -158,111 +146,21 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>201299587</t>
-  </si>
-  <si>
-    <t>135251166</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135251166 - DANIEL RAMIRO HIMELGRYN</t>
-  </si>
-  <si>
-    <t>202697656</t>
-  </si>
-  <si>
-    <t>135287171</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135287171 - SANDERSON LUIS DA SILVA</t>
-  </si>
-  <si>
-    <t>paulo@maceratacorretora.com.br</t>
-  </si>
-  <si>
-    <t>202705954</t>
-  </si>
-  <si>
-    <t>135286167</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135286167 - GABRIEL MONTEZUMA ALVES DE SOUZA</t>
-  </si>
-  <si>
-    <t>203073246</t>
-  </si>
-  <si>
-    <t>135296628</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135296628 - VICTOR HUGO BOZELLI</t>
-  </si>
-  <si>
-    <t>203121011</t>
-  </si>
-  <si>
-    <t>135296967</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135296967 - JOSE MARCELO PIERINI ANIBAL</t>
-  </si>
-  <si>
-    <t>cravinhos.seguros@metalnet.com.br</t>
-  </si>
-  <si>
-    <t>203205996</t>
-  </si>
-  <si>
-    <t>135252696</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135252696 - THAUS RIBEIRO</t>
-  </si>
-  <si>
-    <t>maisseguros@maisseguros.net.be</t>
-  </si>
-  <si>
-    <t>203361674</t>
-  </si>
-  <si>
-    <t>132904067</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 132904067 - JULIO CESAR SOUZA DA ROCHA</t>
-  </si>
-  <si>
-    <t>203466069</t>
-  </si>
-  <si>
-    <t>135304538</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135304538 - ELITOM SALVADOR FURLAN HIJANO</t>
-  </si>
-  <si>
-    <t>willian@nrdc.com.br</t>
-  </si>
-  <si>
-    <t>203952001</t>
-  </si>
-  <si>
-    <t>135190266</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135190266 - JOSE IEDO LUCHO JUNIOR</t>
-  </si>
-  <si>
-    <t>905445767</t>
-  </si>
-  <si>
-    <t>133707855</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 133707855 - MARCILIO FRANCISCO DO NASCIMENTO</t>
+    <t>196907764</t>
+  </si>
+  <si>
+    <t>135190231</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135190231 - FONSATTI ADVOGADOS ASSOCIADOS</t>
+  </si>
+  <si>
+    <t>falecom@nobrecorretora.com.br</t>
   </si>
   <si>
     <t>Prezado(a), _x000D_
 _x000D_
-Identificamos uma falha no processo de cobrança da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+Identificamos uma falha no processo de cobrança da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
 _x000D_
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
 _x000D_
@@ -274,18 +172,75 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>967701586</t>
-  </si>
-  <si>
-    <t>134782328</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 134782328 - LOUJEIN EL CHARITI</t>
+    <t>202900753</t>
+  </si>
+  <si>
+    <t>135292086</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135292086 - ANA LUCIA DE BARROS ARAUJO</t>
+  </si>
+  <si>
+    <t>backoffice1@multicontratar.com.br</t>
+  </si>
+  <si>
+    <t>203326990</t>
+  </si>
+  <si>
+    <t>135300502</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135300502 - ANA PAULA DA SILVA SANTANA</t>
+  </si>
+  <si>
+    <t>204200863</t>
+  </si>
+  <si>
+    <t>135296017</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135296017 - RODRIGO ZILLI</t>
+  </si>
+  <si>
+    <t>204240893</t>
+  </si>
+  <si>
+    <t>135288615</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135288615 - ANDRE RICARDO VIPYCH</t>
+  </si>
+  <si>
+    <t>nobisseg@gmail.com</t>
+  </si>
+  <si>
+    <t>204243632</t>
+  </si>
+  <si>
+    <t>135269113</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135269113 - CEZAR ROBERTO ROSALI</t>
+  </si>
+  <si>
+    <t>hsbsegs@gmail.com</t>
+  </si>
+  <si>
+    <t>230050480</t>
+  </si>
+  <si>
+    <t>135546885</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135546885 - DOUGLAS ZANONI</t>
+  </si>
+  <si>
+    <t>servare@servareseg.com.br</t>
   </si>
   <si>
     <t>Prezado(a), _x000D_
 _x000D_
-Identificamos uma falha no processo de cobrança da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+Identificamos uma falha no processo de cobrança da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
 _x000D_
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
 _x000D_
@@ -295,6 +250,312 @@
 Departamento de Cobrança_x000D_
 _x000D_
 "Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>230219911</t>
+  </si>
+  <si>
+    <t>134231851</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134231851 - IURI GOULART FITZ</t>
+  </si>
+  <si>
+    <t>sustentare@sustentareseguros.com.br</t>
+  </si>
+  <si>
+    <t>230481446</t>
+  </si>
+  <si>
+    <t>135756436</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135756436 - RICARDO FRANCISCO REIS DA SILVA</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>230572665</t>
+  </si>
+  <si>
+    <t>135757683</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135757683 - MAGDA LETICYA DO CARMO</t>
+  </si>
+  <si>
+    <t>prosegrs@proseg.com.br</t>
+  </si>
+  <si>
+    <t>884239645</t>
+  </si>
+  <si>
+    <t>133334744</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 133334744 - CESAR AUGUSTO DOS SANTOS SILVESTRE</t>
+  </si>
+  <si>
+    <t>suporteauto@grupoassure.com.br</t>
+  </si>
+  <si>
+    <t>Prezado(a), _x000D_
+_x000D_
+Identificamos uma falha no processo de cobrança da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+_x000D_
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
+_x000D_
+Pedimos desculpas pelo transtorno causado._x000D_
+_x000D_
+Att._x000D_
+Departamento de Cobrança_x000D_
+_x000D_
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>934220405</t>
+  </si>
+  <si>
+    <t>Prezado(a), _x000D_
+_x000D_
+Identificamos uma falha no processo de cobrança da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+_x000D_
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
+_x000D_
+Pedimos desculpas pelo transtorno causado._x000D_
+_x000D_
+Att._x000D_
+Departamento de Cobrança_x000D_
+_x000D_
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>194800474</t>
+  </si>
+  <si>
+    <t>135155028</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155028 - BASEGGIO DA SILVA TRANSPORTES LTDA EPP</t>
+  </si>
+  <si>
+    <t>194800854</t>
+  </si>
+  <si>
+    <t>135154951</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135154951 - JOSE LUCIANO DA MOTA SILVA</t>
+  </si>
+  <si>
+    <t>caca@valleseguros.srv.br</t>
+  </si>
+  <si>
+    <t>194818609</t>
+  </si>
+  <si>
+    <t>135155478</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155478 - MISAEL PEREIRA DO CARMO</t>
+  </si>
+  <si>
+    <t>segurosbianco@gmail.com</t>
+  </si>
+  <si>
+    <t>194819649</t>
+  </si>
+  <si>
+    <t>135155362</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155362 - VERA LUCIA DE OLIVEIRA GODINHO LEITE</t>
+  </si>
+  <si>
+    <t>educapitoni@gmail.com</t>
+  </si>
+  <si>
+    <t>194819748</t>
+  </si>
+  <si>
+    <t>135155355</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155355 - ELISEU JORGE DA CRUZ</t>
+  </si>
+  <si>
+    <t>processo@previu.com.br</t>
+  </si>
+  <si>
+    <t>194841197</t>
+  </si>
+  <si>
+    <t>135155979</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155979 - LUIZ CARLOS COUTO</t>
+  </si>
+  <si>
+    <t>bernardocorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>194842799</t>
+  </si>
+  <si>
+    <t>135155843</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155843 - KALINCA LIMA MONTEIRO</t>
+  </si>
+  <si>
+    <t>rodrigo.k@fedrizziseguros.com.br</t>
+  </si>
+  <si>
+    <t>194874305</t>
+  </si>
+  <si>
+    <t>135156210</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135156210 - OSCAR DE SOUZA COBRA</t>
+  </si>
+  <si>
+    <t>denis@jphdiascorretora.com.br</t>
+  </si>
+  <si>
+    <t>194875567</t>
+  </si>
+  <si>
+    <t>135156149</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135156149 - FELIPE CORDEIRO GONDIM DE PAIVA</t>
+  </si>
+  <si>
+    <t>paulojurema@gmail.com</t>
+  </si>
+  <si>
+    <t>194898403</t>
+  </si>
+  <si>
+    <t>135157485</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135157485 - HELENITA RIBEIRO SILVA</t>
+  </si>
+  <si>
+    <t>damiciseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>194901579</t>
+  </si>
+  <si>
+    <t>135157372</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135157372 - JOAO SAMPAIO COELHO</t>
+  </si>
+  <si>
+    <t>johnscorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>194906560</t>
+  </si>
+  <si>
+    <t>135157121</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135157121 - IRENE KRAUSE DE AZEVEDO GARCIA</t>
+  </si>
+  <si>
+    <t>irenekrause@hotmail.com</t>
+  </si>
+  <si>
+    <t>194907337</t>
+  </si>
+  <si>
+    <t>135157048</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135157048 - MARINETE DE JESUS CORREA BORGES COSTA</t>
+  </si>
+  <si>
+    <t>adm.perrotseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>195247907</t>
+  </si>
+  <si>
+    <t>135155906</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135155906 - ERNESTINA RODRIGUES SANTANA</t>
+  </si>
+  <si>
+    <t>pratacorretagem@gmail.com</t>
+  </si>
+  <si>
+    <t>195470566</t>
+  </si>
+  <si>
+    <t>135156888</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135156888 - ALCINDO MARCHI</t>
+  </si>
+  <si>
+    <t>camilo@riosegon.com.br</t>
+  </si>
+  <si>
+    <t>195494020</t>
+  </si>
+  <si>
+    <t>135154960</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135154960 - ROSANE DE VARGAS</t>
+  </si>
+  <si>
+    <t>operacional@hpeseguros.com.br</t>
+  </si>
+  <si>
+    <t>967419387</t>
+  </si>
+  <si>
+    <t>134826768</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134826768 - MARCOS ANTONIO FAVA JUNIOR</t>
+  </si>
+  <si>
+    <t>pendencia@vilavelha.com.br</t>
+  </si>
+  <si>
+    <t>Prezado(a), _x000D_
+_x000D_
+Identificamos uma falha no processo de cobrança da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+_x000D_
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
+_x000D_
+Pedimos desculpas pelo transtorno causado._x000D_
+_x000D_
+Att._x000D_
+Departamento de Cobrança_x000D_
+_x000D_
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>967668868</t>
+  </si>
+  <si>
+    <t>134780709</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134780709 - TATIANA GALVAO FERREIRA</t>
+  </si>
+  <si>
+    <t>corretora@alcadacorretora.com</t>
   </si>
 </sst>
 </file>
@@ -781,7 +1042,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="2" customWidth="1" collapsed="1"/>
@@ -868,46 +1129,46 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="15" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>37</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>20</v>
@@ -918,46 +1179,46 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>37</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>20</v>
@@ -968,46 +1229,46 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="O4" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>20</v>
@@ -1018,46 +1279,46 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>20</v>
@@ -1068,46 +1329,46 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>20</v>
@@ -1118,46 +1379,46 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="O7" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>20</v>
@@ -1168,46 +1429,46 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="O8" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>20</v>
@@ -1218,46 +1479,46 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="O9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="15" t="s">
         <v>61</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>37</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>20</v>
@@ -1271,28 +1532,28 @@
         <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>64</v>
@@ -1301,13 +1562,13 @@
         <v>65</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>20</v>
@@ -1321,43 +1582,43 @@
         <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>67</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>20</v>
@@ -1368,46 +1629,46 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>20</v>
@@ -1418,51 +1679,1001 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="S13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q21" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q27" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q31" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S32" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1489,31 +2700,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/DuplicadoRecibos.xlsx
+++ b/Treinamento/DuplicadoRecibos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AE6928-870F-4AB8-B2AD-3E65701B67C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BC9E81-574C-43E2-8D2A-DA3C14CC94C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="256">
   <si>
     <t>msg</t>
   </si>
@@ -96,21 +96,12 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>200389470</t>
-  </si>
-  <si>
-    <t>26/01/2026</t>
-  </si>
-  <si>
     <t>Sim</t>
   </si>
   <si>
     <t>Apólice</t>
   </si>
   <si>
-    <t>135234578</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -118,12 +109,6 @@
   </si>
   <si>
     <t>7-Outros</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135234578 - PEDRO LUIZ DE LUCA FILHO</t>
-  </si>
-  <si>
-    <t>centraleamigos@centraleamigos.com.br</t>
   </si>
   <si>
     <t>57</t>
@@ -146,157 +131,13 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>207882956</t>
-  </si>
-  <si>
-    <t>135370894</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135370894 - ARLENE DE OLIVEIRA R</t>
-  </si>
-  <si>
-    <t>autore@g4seguros.com.br</t>
-  </si>
-  <si>
-    <t>207946199</t>
-  </si>
-  <si>
-    <t>135365144</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135365144 - JOSE LUIZ ZOBOLI</t>
-  </si>
-  <si>
-    <t>tower@towercorretora.com.br</t>
-  </si>
-  <si>
-    <t>207950027</t>
-  </si>
-  <si>
-    <t>135364580</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135364580 - MAURO LUIZ VENTURINI</t>
-  </si>
-  <si>
-    <t>atendimento.doeste@gmail.com</t>
-  </si>
-  <si>
-    <t>207987136</t>
-  </si>
-  <si>
-    <t>135362622</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135362622 - EVANDRO CESAR TERRON</t>
-  </si>
-  <si>
-    <t>contato@gdseguros.com.br</t>
-  </si>
-  <si>
-    <t>207995758</t>
-  </si>
-  <si>
-    <t>135361512</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135361512 - EDSON MEDINA</t>
-  </si>
-  <si>
-    <t>vizi2009@hotmail.com</t>
-  </si>
-  <si>
-    <t>208039978</t>
-  </si>
-  <si>
-    <t>135358481</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135358481 - SARA OLIVEIRA MONTEIRO DE BARROS</t>
-  </si>
-  <si>
-    <t>atendimento@barrabellaseguros.com.br</t>
-  </si>
-  <si>
-    <t>208142830</t>
-  </si>
-  <si>
-    <t>135379254</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135379254 - NAFITALIM CARLOS DOS ANJOS SOUSA</t>
-  </si>
-  <si>
     <t>maxsegur@maxsegur.com.br</t>
   </si>
   <si>
-    <t>208215966</t>
-  </si>
-  <si>
-    <t>135379626</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135379626 - FERNANDA FAGUNDES FERREIRA</t>
-  </si>
-  <si>
     <t>sustentare@sustentareseguros.com.br</t>
   </si>
   <si>
-    <t>208281067</t>
-  </si>
-  <si>
-    <t>135273252</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135273252 - LUCIANA DANTAS FERNA</t>
-  </si>
-  <si>
-    <t>contato@saobentoseguros.com.br</t>
-  </si>
-  <si>
-    <t>208281471</t>
-  </si>
-  <si>
-    <t>135269689</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135269689 - PAULO RODRIGO MIGUEL</t>
-  </si>
-  <si>
-    <t>queiti.fischer.seguros@unidascorp.com.br</t>
-  </si>
-  <si>
-    <t>208652663</t>
-  </si>
-  <si>
-    <t>135389223</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135389223 - THIAGO CANDIDO BLANC</t>
-  </si>
-  <si>
-    <t>i5seg@i5segseguros.com.br</t>
-  </si>
-  <si>
-    <t>208688295</t>
-  </si>
-  <si>
-    <t>135390192</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135390192 - MAURICE MIGUEL BARROS MORENO</t>
-  </si>
-  <si>
     <t>backoffice1@multicontratar.com.br</t>
-  </si>
-  <si>
-    <t>229849595</t>
-  </si>
-  <si>
-    <t>135744132</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135744132 - PAULA DE MELO JORGE</t>
   </si>
   <si>
     <t>Prezado(a), _x000D_
@@ -313,309 +154,25 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>231662853</t>
-  </si>
-  <si>
-    <t>135775042</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135775042 - GIZELIA AZEVEDO DA TRINDADE BRANDAO</t>
-  </si>
-  <si>
     <t>tungstenio.corretora@hotmail.com</t>
   </si>
   <si>
-    <t>232015465</t>
-  </si>
-  <si>
-    <t>135762915</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135762915 - ANTONIA MONALIZA SOARES LOPES</t>
-  </si>
-  <si>
-    <t>232278188</t>
-  </si>
-  <si>
-    <t>135772873</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135772873 - CARLITO OLIVEIRA</t>
-  </si>
-  <si>
     <t>tecnica@perspectivaseguros.com.br</t>
   </si>
   <si>
-    <t>232347009</t>
-  </si>
-  <si>
-    <t>135784328</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135784328 - GILBERTO DE ARAUJO SILVA</t>
-  </si>
-  <si>
-    <t>233096852</t>
-  </si>
-  <si>
-    <t>135801430</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135801430 - ROMILDO CELIN</t>
-  </si>
-  <si>
-    <t>233260417</t>
-  </si>
-  <si>
-    <t>135786092</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135786092 - RICARDO DE SOUZA AMORIM</t>
-  </si>
-  <si>
-    <t>233490600</t>
-  </si>
-  <si>
-    <t>135803683</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135803683 - NARIELLY KARINNY DE ARAUJO SILVA CUNHA</t>
-  </si>
-  <si>
-    <t>234656027</t>
-  </si>
-  <si>
-    <t>135826910</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135826910 - WAGNER DE ALMEIDA PAIVA</t>
-  </si>
-  <si>
-    <t>234755605</t>
-  </si>
-  <si>
-    <t>135828885</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135828885 - BRUNO SCARPAT</t>
-  </si>
-  <si>
-    <t>235474800</t>
-  </si>
-  <si>
-    <t>135846655</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135846655 - VERONI DE SOUZA CAMPOS</t>
-  </si>
-  <si>
     <t>vjomm@vipdinamica.com.br</t>
   </si>
   <si>
-    <t>235514696</t>
-  </si>
-  <si>
-    <t>135846739</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135846739 - ELIAS HANAUER ME</t>
-  </si>
-  <si>
-    <t>235888751</t>
-  </si>
-  <si>
-    <t>135847617</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135847617 - HELDER BORBA NOGUEIRA</t>
-  </si>
-  <si>
-    <t>235899758</t>
-  </si>
-  <si>
-    <t>135846226</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135846226 - EVELLYN CRISTINA LOC</t>
-  </si>
-  <si>
     <t>falecom@nobrecorretora.com.br</t>
   </si>
   <si>
-    <t>235900978</t>
-  </si>
-  <si>
-    <t>135846146</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135846146 - LEANDRO BRITES APOLINARIO</t>
-  </si>
-  <si>
-    <t>cifarelliseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>235941477</t>
-  </si>
-  <si>
-    <t>135840786</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135840786 - DENIS RICARDO RODRIGUES DE SOUZA</t>
-  </si>
-  <si>
     <t>vipmares.corretora@gmail.com</t>
   </si>
   <si>
-    <t>236002808</t>
-  </si>
-  <si>
-    <t>135832049</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135832049 - ROSEMARY APARECIDA ZEQUIM LUIZAO</t>
-  </si>
-  <si>
     <t>plinio@corretoratotal.com.br</t>
   </si>
   <si>
-    <t>236008839</t>
-  </si>
-  <si>
-    <t>135831025</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135831025 - TAINA BRITO JORDANI CEOLIN</t>
-  </si>
-  <si>
-    <t>jackson@silveiracorretora.com</t>
-  </si>
-  <si>
-    <t>236028092</t>
-  </si>
-  <si>
-    <t>135848532</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135848532 - JOSE APARECIDO BASTASINI</t>
-  </si>
-  <si>
-    <t>236029132</t>
-  </si>
-  <si>
-    <t>135848486</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135848486 - JOAO ANTONIO MACHADO DUTRA</t>
-  </si>
-  <si>
-    <t>236051011</t>
-  </si>
-  <si>
-    <t>135825538</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135825538 - HYAGO VIEIRA DE SOUZ</t>
-  </si>
-  <si>
-    <t>sicaracorretora@gmail.com</t>
-  </si>
-  <si>
-    <t>236065235</t>
-  </si>
-  <si>
-    <t>135824513</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135824513 - ISABEL CRISTINA TEIXEIRA DE CASTRO</t>
-  </si>
-  <si>
     <t>sudeste@sudesteseguros.com.br</t>
-  </si>
-  <si>
-    <t>236067173</t>
-  </si>
-  <si>
-    <t>135817641</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135817641 - REGINA FRANCISCA DURAES</t>
-  </si>
-  <si>
-    <t>236074468</t>
-  </si>
-  <si>
-    <t>135752470</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135752470 - PHILIPPE RIBEIRO CASSIANO DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>atendimento@humberseguros.com.br</t>
-  </si>
-  <si>
-    <t>236074583</t>
-  </si>
-  <si>
-    <t>135752047</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135752047 - SELMA TAVARES DOS SANTOS LOPES</t>
-  </si>
-  <si>
-    <t>236075101</t>
-  </si>
-  <si>
-    <t>135655797</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135655797 - ELIAS RAFAEL MIRANDA RIBEIRO</t>
-  </si>
-  <si>
-    <t>cadastro@theoneseguros.com.br</t>
-  </si>
-  <si>
-    <t>236084509</t>
-  </si>
-  <si>
-    <t>135848980</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 135848980 - JANE CRISTINA RAVANHANI GOMES</t>
-  </si>
-  <si>
-    <t>812360893</t>
-  </si>
-  <si>
-    <t>132068387</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 132068387 - THAIANA VIANA RODRIGUES</t>
-  </si>
-  <si>
-    <t>Prezado(a), _x000D_
-_x000D_
-Identificamos uma falha no processo de cobrança da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
-_x000D_
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
-_x000D_
-Pedimos desculpas pelo transtorno causado._x000D_
-_x000D_
-Att._x000D_
-Departamento de Cobrança_x000D_
-_x000D_
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>834985560</t>
-  </si>
-  <si>
-    <t>132462988</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 132462988 - DANIELA APARECIDA DE GODOI GONCALVES</t>
-  </si>
-  <si>
-    <t>premium.seguros@uol.com.br</t>
   </si>
   <si>
     <t>Prezado(a), _x000D_
@@ -632,80 +189,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>837016058</t>
-  </si>
-  <si>
-    <t>132502538</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 132502538 - CARLOS UMBERTO DA SILVA</t>
-  </si>
-  <si>
-    <t>carlos@eurocorretora.com</t>
-  </si>
-  <si>
-    <t>838322281</t>
-  </si>
-  <si>
-    <t>132529369</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 132529369 - CORALIA GABRIELLE VIEIRA SILVEIRA</t>
-  </si>
-  <si>
-    <t>jurici@hotmail.com</t>
-  </si>
-  <si>
-    <t>838565475</t>
-  </si>
-  <si>
-    <t>132146349</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 132146349 - UBIRAJARA DE ARAUJO GOMES PEREIRA</t>
-  </si>
-  <si>
-    <t>936279037</t>
-  </si>
-  <si>
-    <t>134265629</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 134265629 - ANDREA HELENA GONZAGA CARDOSO</t>
-  </si>
-  <si>
-    <t>Prezado(a), _x000D_
-_x000D_
-Identificamos uma falha no processo de cobrança da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
-_x000D_
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
-_x000D_
-Pedimos desculpas pelo transtorno causado._x000D_
-_x000D_
-Att._x000D_
-Departamento de Cobrança_x000D_
-_x000D_
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>945904047</t>
-  </si>
-  <si>
-    <t>134437315</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 134437315 - SATA TRANSPORTES LTDA EPP</t>
-  </si>
-  <si>
-    <t>972192425</t>
-  </si>
-  <si>
-    <t>134846826</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 134846826 - EMERSON TONIETO</t>
-  </si>
-  <si>
     <t>Prezado(a), _x000D_
 _x000D_
 Identificamos uma falha no processo de cobrança da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
@@ -720,27 +203,9 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>972383594</t>
-  </si>
-  <si>
-    <t>134909573</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 134909573 - JULIANA CAMILA SILVA</t>
-  </si>
-  <si>
     <t>prosegrs@proseg.com.br</t>
   </si>
   <si>
-    <t>972610459</t>
-  </si>
-  <si>
-    <t>133743675</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 133743675 - RICARDO DA SILVA SANTOS</t>
-  </si>
-  <si>
     <t>194803106</t>
   </si>
   <si>
@@ -796,6 +261,610 @@
   </si>
   <si>
     <t>seguradora@minutoseguros.com.br</t>
+  </si>
+  <si>
+    <t>209056146</t>
+  </si>
+  <si>
+    <t>27/01/2026</t>
+  </si>
+  <si>
+    <t>135388881</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135388881 - JACO VITOR BUSSOLO</t>
+  </si>
+  <si>
+    <t>unicinco@unicinco.com.br</t>
+  </si>
+  <si>
+    <t>209108160</t>
+  </si>
+  <si>
+    <t>135383223</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135383223 - JOSINALDO FRANCISCO DA SILVA</t>
+  </si>
+  <si>
+    <t>209216880</t>
+  </si>
+  <si>
+    <t>135397167</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135397167 - WEDJA RAFAELA CAMPOS DE MOURA</t>
+  </si>
+  <si>
+    <t>209371560</t>
+  </si>
+  <si>
+    <t>135378486</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135378486 - JULIANO CARDOSO SATH</t>
+  </si>
+  <si>
+    <t>lucas.bhseg@gmail.com</t>
+  </si>
+  <si>
+    <t>209486236</t>
+  </si>
+  <si>
+    <t>135370725</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135370725 - ALINE MARA MENDES DO</t>
+  </si>
+  <si>
+    <t>corretora@camedseguros.com.br</t>
+  </si>
+  <si>
+    <t>209505266</t>
+  </si>
+  <si>
+    <t>135367020</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135367020 - JULIO CESAR GONCALVE</t>
+  </si>
+  <si>
+    <t>emerson@jubileucorretoradeseguros.com.br</t>
+  </si>
+  <si>
+    <t>209506686</t>
+  </si>
+  <si>
+    <t>135365732</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135365732 - MARCO ANTONIO MANSO CARIUS</t>
+  </si>
+  <si>
+    <t>elo@eloseguros.com.br</t>
+  </si>
+  <si>
+    <t>209545890</t>
+  </si>
+  <si>
+    <t>135341991</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135341991 - SAMIRA DE LIMA CHAHI</t>
+  </si>
+  <si>
+    <t>ney@participativa.com.br</t>
+  </si>
+  <si>
+    <t>209549918</t>
+  </si>
+  <si>
+    <t>135335438</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135335438 - ADRIANA MARA CHAVES</t>
+  </si>
+  <si>
+    <t>itajubaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>209577620</t>
+  </si>
+  <si>
+    <t>135322810</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135322810 - PEDRO SOARES FERREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>paula.antonucci@antonucciseguros.com.br</t>
+  </si>
+  <si>
+    <t>209582513</t>
+  </si>
+  <si>
+    <t>135285350</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135285350 - ROBERTO TALES GARCIA</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>209583156</t>
+  </si>
+  <si>
+    <t>135274475</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135274475 - PETERSON BAUNGARTNER</t>
+  </si>
+  <si>
+    <t>luma@piracemaseguros.com.br</t>
+  </si>
+  <si>
+    <t>209654718</t>
+  </si>
+  <si>
+    <t>135404927</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135404927 - NORMA FREITAS CHAVES</t>
+  </si>
+  <si>
+    <t>209688146</t>
+  </si>
+  <si>
+    <t>135406218</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135406218 - EVERTON MARTINS DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>209928716</t>
+  </si>
+  <si>
+    <t>135412099</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135412099 - CLEVENICIA APARECIDA FERREIRA DOURADO</t>
+  </si>
+  <si>
+    <t>209985872</t>
+  </si>
+  <si>
+    <t>135412847</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135412847 - KAIRO RODRIGO DA SILVA GRANJEIRO</t>
+  </si>
+  <si>
+    <t>209991722</t>
+  </si>
+  <si>
+    <t>135353297</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135353297 - ELISETE MARLI OST</t>
+  </si>
+  <si>
+    <t>210001834</t>
+  </si>
+  <si>
+    <t>135413316</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135413316 - DANIEL LIMA</t>
+  </si>
+  <si>
+    <t>222647582</t>
+  </si>
+  <si>
+    <t>135613657</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135613657 - MARCUS VINICIUS RAMOS COELHO</t>
+  </si>
+  <si>
+    <t>flavio.firbida@hotmail.com</t>
+  </si>
+  <si>
+    <t>224253140</t>
+  </si>
+  <si>
+    <t>135648005</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135648005 - MARCIO CAMILO ALBUQUERQUE MELO</t>
+  </si>
+  <si>
+    <t>230614186</t>
+  </si>
+  <si>
+    <t>135752594</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135752594 - CRELSON JORGE ESTOLANO CABRAL</t>
+  </si>
+  <si>
+    <t>231556626</t>
+  </si>
+  <si>
+    <t>135773070</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135773070 - JANE MARIA BOCORNY BORDIN</t>
+  </si>
+  <si>
+    <t>alex@wteixeiraseguros.com.br</t>
+  </si>
+  <si>
+    <t>231657093</t>
+  </si>
+  <si>
+    <t>135775306</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135775306 - ROSA MARIE EKO BURG</t>
+  </si>
+  <si>
+    <t>231841929</t>
+  </si>
+  <si>
+    <t>135779050</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135779050 - DALVA PAIVA SANTOS MARTINEZ</t>
+  </si>
+  <si>
+    <t>231939087</t>
+  </si>
+  <si>
+    <t>135775378</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135775378 - TAISE SAIONARA DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>232247167</t>
+  </si>
+  <si>
+    <t>135775658</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135775658 - DANIELA MENDES DOS SANTOS VIEGAS</t>
+  </si>
+  <si>
+    <t>232836985</t>
+  </si>
+  <si>
+    <t>135795533</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135795533 - CLAUDIMIR ANTONIO CHRIST</t>
+  </si>
+  <si>
+    <t>234260200</t>
+  </si>
+  <si>
+    <t>135822386</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135822386 - MARILZA BARBOZA PRADO LOPES</t>
+  </si>
+  <si>
+    <t>234850034</t>
+  </si>
+  <si>
+    <t>135831126</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135831126 - ROSANGELA SILVA DA CUNHA NICOLAU</t>
+  </si>
+  <si>
+    <t>suporteauto@grupoassure.com.br</t>
+  </si>
+  <si>
+    <t>234999310</t>
+  </si>
+  <si>
+    <t>135776328</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135776328 - SERGIO ROMERO MEDEIROS ESCOREL RIBEIRO</t>
+  </si>
+  <si>
+    <t>tacarunaseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>235347493</t>
+  </si>
+  <si>
+    <t>135843642</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135843642 - FLAVIO SILVA FLORENCIO</t>
+  </si>
+  <si>
+    <t>235379595</t>
+  </si>
+  <si>
+    <t>135842654</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135842654 - VERCILAU GAVA</t>
+  </si>
+  <si>
+    <t>235466517</t>
+  </si>
+  <si>
+    <t>135843715</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135843715 - ANDREA CRISTINA TEIXEIRA SALES SILVA</t>
+  </si>
+  <si>
+    <t>jamil@jamilseguros.com</t>
+  </si>
+  <si>
+    <t>235625385</t>
+  </si>
+  <si>
+    <t>135840647</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135840647 - ADILSON LUIZ FUNEZ</t>
+  </si>
+  <si>
+    <t>235645896</t>
+  </si>
+  <si>
+    <t>135836914</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135836914 - IVAN LUCIO DA SILVEIRA</t>
+  </si>
+  <si>
+    <t>235933417</t>
+  </si>
+  <si>
+    <t>135841726</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135841726 - ODON OLIVEIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>235963935</t>
+  </si>
+  <si>
+    <t>135837294</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135837294 - CONSTANCIA LIRA DE BARROS CORREIA RODRIGUES C</t>
+  </si>
+  <si>
+    <t>236290098</t>
+  </si>
+  <si>
+    <t>135822643</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135822643 - DEIVI BENTO BITTENCOURT</t>
+  </si>
+  <si>
+    <t>coligacao@coligacaoseguros.com.br</t>
+  </si>
+  <si>
+    <t>236297317</t>
+  </si>
+  <si>
+    <t>135822029</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135822029 - DULCELEIA GOMES CASSIANO</t>
+  </si>
+  <si>
+    <t>236328856</t>
+  </si>
+  <si>
+    <t>135819498</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135819498 - FERNANDO PINHEIRO LARICA</t>
+  </si>
+  <si>
+    <t>236343673</t>
+  </si>
+  <si>
+    <t>135818344</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135818344 - WILLIAN TRINDADE FERREIRA</t>
+  </si>
+  <si>
+    <t>236371849</t>
+  </si>
+  <si>
+    <t>135815922</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135815922 - THAMIRES BRAUM PEREIRA</t>
+  </si>
+  <si>
+    <t>236379248</t>
+  </si>
+  <si>
+    <t>135815289</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135815289 - IZAIAS TORRES GALINDO</t>
+  </si>
+  <si>
+    <t>236392969</t>
+  </si>
+  <si>
+    <t>135814322</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135814322 - IZABEL ANTUNES</t>
+  </si>
+  <si>
+    <t>236422006</t>
+  </si>
+  <si>
+    <t>135811600</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135811600 - PAULO HENRIQUE SILVA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>236454082</t>
+  </si>
+  <si>
+    <t>133469362</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 133469362 - EVERSON FERNANDES ATHAYDE</t>
+  </si>
+  <si>
+    <t>236465641</t>
+  </si>
+  <si>
+    <t>135807649</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135807649 - LIVIA CUNHA GALVAO DE FRANCA</t>
+  </si>
+  <si>
+    <t>236474411</t>
+  </si>
+  <si>
+    <t>135806934</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135806934 - WILSON ROBERTO NAVARRO</t>
+  </si>
+  <si>
+    <t>236514331</t>
+  </si>
+  <si>
+    <t>135800127</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 135800127 - VO MIRO TRANSPORTES RODOVIARIOS LTDA EPP</t>
+  </si>
+  <si>
+    <t>770343501</t>
+  </si>
+  <si>
+    <t>131347630</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 131347630 - CLAUDIO GOMES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>tecnica@pvscorretora.com.br</t>
+  </si>
+  <si>
+    <t>Prezado(a), _x000D_
+_x000D_
+Identificamos uma falha no processo de cobrança da parcela 12 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+_x000D_
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
+_x000D_
+Pedimos desculpas pelo transtorno causado._x000D_
+_x000D_
+Att._x000D_
+Departamento de Cobrança_x000D_
+_x000D_
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>912804410</t>
+  </si>
+  <si>
+    <t>133841834</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 133841834 - ALEXANDRA GEVEHR</t>
+  </si>
+  <si>
+    <t>Prezado(a), _x000D_
+_x000D_
+Identificamos uma falha no processo de cobrança da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se em anexo e disponível na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador._x000D_
+_x000D_
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do Gestor de Operações._x000D_
+_x000D_
+Pedimos desculpas pelo transtorno causado._x000D_
+_x000D_
+Att._x000D_
+Departamento de Cobrança_x000D_
+_x000D_
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>917034690</t>
+  </si>
+  <si>
+    <t>133921513</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 133921513 - JOSE MAURILIO DE BARROS E SA</t>
+  </si>
+  <si>
+    <t>917359071</t>
+  </si>
+  <si>
+    <t>133925988</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 133925988 - CENIR MORAES DE MIRANDA</t>
+  </si>
+  <si>
+    <t>917816369</t>
+  </si>
+  <si>
+    <t>133935235</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 133935235 - FABIO REBOUCAS DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>971362904</t>
+  </si>
+  <si>
+    <t>134885161</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134885161 - FABIO JOSE SIMOES DE MATOS</t>
+  </si>
+  <si>
+    <t>972201325</t>
+  </si>
+  <si>
+    <t>134905533</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134905533 - MARCIA SOLANGE MODOLO XAVIER</t>
+  </si>
+  <si>
+    <t>973594454</t>
+  </si>
+  <si>
+    <t>134926109</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134926109 - HERTHA GOTTEMS</t>
+  </si>
+  <si>
+    <t>973789559</t>
+  </si>
+  <si>
+    <t>134926211</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 134926211 - ANDRE SIMI GIACOMELLI</t>
   </si>
 </sst>
 </file>
@@ -1282,7 +1351,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="2" customWidth="1" collapsed="1"/>
@@ -1369,46 +1438,46 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>20</v>
@@ -1419,46 +1488,46 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>20</v>
@@ -1469,46 +1538,46 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>20</v>
@@ -1519,46 +1588,46 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>20</v>
@@ -1569,46 +1638,46 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>20</v>
@@ -1619,46 +1688,46 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>20</v>
@@ -1669,46 +1738,46 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>20</v>
@@ -1719,46 +1788,46 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>20</v>
@@ -1769,46 +1838,46 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>20</v>
@@ -1819,46 +1888,46 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>20</v>
@@ -1869,46 +1938,46 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>20</v>
@@ -1919,46 +1988,46 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>20</v>
@@ -1969,46 +2038,46 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q14" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>20</v>
@@ -2019,46 +2088,46 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q15" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q15" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>20</v>
@@ -2069,46 +2138,46 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>20</v>
@@ -2119,46 +2188,46 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>20</v>
@@ -2169,46 +2238,46 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>20</v>
@@ -2219,46 +2288,46 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>20</v>
@@ -2269,46 +2338,46 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>20</v>
@@ -2319,46 +2388,46 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q21" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>20</v>
@@ -2369,46 +2438,46 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q22" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>20</v>
@@ -2419,46 +2488,46 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q23" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>20</v>
@@ -2469,46 +2538,46 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q24" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>20</v>
@@ -2519,46 +2588,46 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q25" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>20</v>
@@ -2569,46 +2638,46 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q26" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q26" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>20</v>
@@ -2619,46 +2688,46 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q27" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q27" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>20</v>
@@ -2669,46 +2738,46 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q28" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q28" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>20</v>
@@ -2719,46 +2788,46 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q29" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>20</v>
@@ -2769,46 +2838,46 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q30" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R30" s="2" t="s">
         <v>20</v>
@@ -2819,46 +2888,46 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q31" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>20</v>
@@ -2869,46 +2938,46 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q32" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q32" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>20</v>
@@ -2919,46 +2988,46 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q33" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q33" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>20</v>
@@ -2969,46 +3038,46 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q34" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q34" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>20</v>
@@ -3019,46 +3088,46 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q35" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>20</v>
@@ -3069,46 +3138,46 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q36" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>20</v>
@@ -3119,46 +3188,46 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q37" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q37" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R37" s="2" t="s">
         <v>20</v>
@@ -3169,46 +3238,46 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q38" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q38" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>20</v>
@@ -3219,46 +3288,46 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q39" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q39" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R39" s="2" t="s">
         <v>20</v>
@@ -3269,46 +3338,46 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q40" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q40" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>20</v>
@@ -3319,46 +3388,46 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q41" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q41" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>20</v>
@@ -3369,46 +3438,46 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q42" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q42" s="15" t="s">
-        <v>179</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>20</v>
@@ -3419,46 +3488,46 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q43" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q43" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="R43" s="2" t="s">
         <v>20</v>
@@ -3469,46 +3538,46 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q44" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q44" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>20</v>
@@ -3519,46 +3588,46 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>192</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q45" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q45" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="R45" s="2" t="s">
         <v>20</v>
@@ -3569,46 +3638,46 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q46" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q46" s="15" t="s">
-        <v>184</v>
       </c>
       <c r="R46" s="2" t="s">
         <v>20</v>
@@ -3619,46 +3688,46 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q47" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q47" s="15" t="s">
-        <v>199</v>
       </c>
       <c r="R47" s="2" t="s">
         <v>20</v>
@@ -3669,46 +3738,46 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q48" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q48" s="15" t="s">
-        <v>199</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>20</v>
@@ -3719,46 +3788,46 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q49" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q49" s="15" t="s">
-        <v>206</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>20</v>
@@ -3769,46 +3838,46 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q50" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="Q50" s="15" t="s">
-        <v>206</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>20</v>
@@ -3819,46 +3888,46 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q51" s="15" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="R51" s="2" t="s">
         <v>20</v>
@@ -3869,46 +3938,46 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>217</v>
+        <v>42</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q52" s="15" t="s">
-        <v>33</v>
+        <v>234</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>20</v>
@@ -3919,46 +3988,46 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q53" s="15" t="s">
-        <v>33</v>
+        <v>234</v>
       </c>
       <c r="R53" s="2" t="s">
         <v>20</v>
@@ -3969,46 +4038,46 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>224</v>
+        <v>42</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q54" s="15" t="s">
-        <v>33</v>
+        <v>234</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>20</v>
@@ -4019,46 +4088,46 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q55" s="15" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>20</v>
@@ -4069,51 +4138,451 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q56" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q57" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q58" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q59" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q60" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q56" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="S56" s="2" t="s">
+      <c r="R60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q61" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q62" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q63" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q64" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S64" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4140,31 +4609,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>